--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.7662,0.0499,0.1496,0.0596</t>
-  </si>
-  <si>
-    <t>0.0233,0.0011,0.0001,0.9929</t>
-  </si>
-  <si>
-    <t>0.7484,0.0124,0.0055,0.2920</t>
-  </si>
-  <si>
-    <t>0.2272,0.0086,0.0044,0.8888</t>
-  </si>
-  <si>
-    <t>0.9881,0.0133,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9897,0.0058,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9796,0.0142,0.0027,0.0022</t>
-  </si>
-  <si>
-    <t>0.9932,0.0058,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9814,0.0251,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9748,0.0316,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9915,0.0061,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9926,0.0028,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.7702,0.0606,0.1347,0.0488</t>
-  </si>
-  <si>
-    <t>0.5700,0.0797,0.4323,0.0133</t>
-  </si>
-  <si>
-    <t>0.6241,0.0298,0.5022,0.0023</t>
-  </si>
-  <si>
-    <t>0.1200,0.0364,0.8652,0.0052</t>
-  </si>
-  <si>
-    <t>0.8252,0.0648,0.1480,0.0056</t>
-  </si>
-  <si>
-    <t>0.0196,0.9337,0.2387,0.0004</t>
-  </si>
-  <si>
-    <t>0.0041,0.9890,0.0098,0.0006</t>
-  </si>
-  <si>
-    <t>0.2106,0.8292,0.0341,0.0026</t>
-  </si>
-  <si>
-    <t>0.0045,0.9826,0.0032,0.0095</t>
-  </si>
-  <si>
-    <t>0.0024,0.9918,0.0151,0.0004</t>
-  </si>
-  <si>
-    <t>0.3642,0.0203,0.5833,0.0817</t>
-  </si>
-  <si>
-    <t>0.3923,0.0274,0.5741,0.0467</t>
-  </si>
-  <si>
-    <t>0.0028,0.0021,0.9943,0.0007</t>
-  </si>
-  <si>
-    <t>0.0606,0.0333,0.8912,0.0169</t>
-  </si>
-  <si>
-    <t>0.1545,0.0028,0.9029,0.0036</t>
-  </si>
-  <si>
-    <t>0.1030,0.0200,0.8944,0.0030</t>
-  </si>
-  <si>
-    <t>0.0237,0.0059,0.9708,0.0052</t>
-  </si>
-  <si>
-    <t>0.2942,0.4893,0.2403,0.0031</t>
-  </si>
-  <si>
-    <t>0.5973,0.2205,0.2107,0.0061</t>
-  </si>
-  <si>
-    <t>0.0012,0.0146,0.9948,0.0023</t>
-  </si>
-  <si>
-    <t>0.0306,0.8108,0.3761,0.0011</t>
-  </si>
-  <si>
-    <t>0.8705,0.0672,0.0450,0.0265</t>
-  </si>
-  <si>
-    <t>0.8799,0.0784,0.0496,0.0087</t>
-  </si>
-  <si>
-    <t>0.5700,0.5671,0.0101,0.0021</t>
-  </si>
-  <si>
-    <t>0.0654,0.8394,0.3189,0.0060</t>
-  </si>
-  <si>
-    <t>0.0093,0.8364,0.7325,0.0083</t>
-  </si>
-  <si>
-    <t>0.0112,0.1176,0.9482,0.0154</t>
-  </si>
-  <si>
-    <t>0.0323,0.0273,0.9569,0.0033</t>
-  </si>
-  <si>
-    <t>0.1927,0.0083,0.8452,0.0094</t>
-  </si>
-  <si>
-    <t>0.0138,0.4267,0.9219,0.0039</t>
-  </si>
-  <si>
-    <t>0.0103,0.9451,0.0726,0.0087</t>
-  </si>
-  <si>
-    <t>0.0048,0.0047,0.9756,0.0378</t>
-  </si>
-  <si>
-    <t>0.0954,0.3319,0.0050,0.8002</t>
-  </si>
-  <si>
-    <t>0.0196,0.9559,0.0048,0.0203</t>
-  </si>
-  <si>
-    <t>0.0197,0.9142,0.3668,0.0043</t>
-  </si>
-  <si>
-    <t>0.0101,0.9672,0.0506,0.0096</t>
-  </si>
-  <si>
-    <t>0.0105,0.6689,0.9001,0.0038</t>
-  </si>
-  <si>
-    <t>0.0012,0.0103,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.1507,0.0173,0.8658,0.0105</t>
-  </si>
-  <si>
-    <t>0.0642,0.0045,0.9524,0.0027</t>
-  </si>
-  <si>
-    <t>0.0010,0.0035,0.9957,0.0023</t>
-  </si>
-  <si>
-    <t>0.0083,0.1190,0.9635,0.0056</t>
-  </si>
-  <si>
-    <t>0.8087,0.2059,0.0138,0.0170</t>
-  </si>
-  <si>
-    <t>0.9306,0.0446,0.0254,0.0069</t>
-  </si>
-  <si>
-    <t>0.9692,0.0244,0.0064,0.0024</t>
-  </si>
-  <si>
-    <t>0.0148,0.4738,0.9421,0.0035</t>
-  </si>
-  <si>
-    <t>0.9880,0.0061,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9854,0.0135,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.7180,0.4201,0.0085,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.6093,0.9873,0.0004</t>
-  </si>
-  <si>
-    <t>0.0338,0.0160,0.9560,0.0065</t>
-  </si>
-  <si>
-    <t>0.0043,0.0062,0.9856,0.0067</t>
-  </si>
-  <si>
-    <t>0.0004,0.9592,0.9294,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0057,0.9940,0.0008</t>
-  </si>
-  <si>
-    <t>0.0342,0.8566,0.1885,0.0010</t>
-  </si>
-  <si>
-    <t>0.0065,0.9894,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.3484,0.2039,0.5927,0.0081</t>
-  </si>
-  <si>
-    <t>0.5249,0.4089,0.1390,0.0102</t>
-  </si>
-  <si>
-    <t>0.0060,0.1067,0.9805,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.8966,0.9041,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.7406,0.9235,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.9754,0.4604,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.8528,0.9545,0.0002</t>
-  </si>
-  <si>
-    <t>0.0314,0.0072,0.0211,0.9699</t>
-  </si>
-  <si>
-    <t>0.0130,0.0020,0.0006,0.9944</t>
-  </si>
-  <si>
-    <t>0.0053,0.0044,0.0001,0.9973</t>
-  </si>
-  <si>
-    <t>0.0265,0.0088,0.0076,0.9801</t>
-  </si>
-  <si>
-    <t>0.0094,0.0203,0.0008,0.9928</t>
-  </si>
-  <si>
-    <t>0.0449,0.0081,0.0006,0.9808</t>
-  </si>
-  <si>
-    <t>0.0012,0.9645,0.8332,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.7976,0.9265,0.0004</t>
-  </si>
-  <si>
-    <t>0.0035,0.7950,0.8956,0.0008</t>
-  </si>
-  <si>
-    <t>0.0046,0.5879,0.9469,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.8031,0.9491,0.0001</t>
-  </si>
-  <si>
-    <t>0.0144,0.6665,0.6886,0.0019</t>
-  </si>
-  <si>
-    <t>0.8422,0.1937,0.0246,0.0017</t>
-  </si>
-  <si>
-    <t>0.9847,0.0139,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9676,0.0392,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9902,0.0038,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9847,0.0129,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9942,0.0054,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9806,0.0180,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9371,0.0900,0.0054,0.0018</t>
-  </si>
-  <si>
-    <t>0.9945,0.0036,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9916,0.0076,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9951,0.0027,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9935,0.0040,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9951,0.0014,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0043,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9868,0.0101,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.0084,0.0009,0.9888,0.0022</t>
-  </si>
-  <si>
-    <t>0.0711,0.0234,0.9210,0.0021</t>
-  </si>
-  <si>
-    <t>0.7055,0.0723,0.1922,0.0363</t>
-  </si>
-  <si>
-    <t>0.2044,0.0157,0.8588,0.0023</t>
-  </si>
-  <si>
-    <t>0.0130,0.9746,0.0023,0.0040</t>
-  </si>
-  <si>
-    <t>0.0055,0.9852,0.0028,0.0022</t>
-  </si>
-  <si>
-    <t>0.0587,0.9279,0.0217,0.0031</t>
-  </si>
-  <si>
-    <t>0.3662,0.6810,0.0325,0.0079</t>
-  </si>
-  <si>
-    <t>0.0343,0.9401,0.0031,0.0146</t>
-  </si>
-  <si>
-    <t>0.0075,0.9804,0.0065,0.0020</t>
-  </si>
-  <si>
-    <t>0.6751,0.4113,0.0254,0.0031</t>
-  </si>
-  <si>
-    <t>0.7466,0.0664,0.2157,0.0133</t>
-  </si>
-  <si>
-    <t>0.7175,0.0109,0.4068,0.0109</t>
-  </si>
-  <si>
-    <t>0.1300,0.7931,0.1523,0.0630</t>
-  </si>
-  <si>
-    <t>0.6286,0.0386,0.4361,0.0134</t>
-  </si>
-  <si>
-    <t>0.6514,0.0568,0.0593,0.3016</t>
-  </si>
-  <si>
-    <t>0.0143,0.9722,0.0403,0.0023</t>
-  </si>
-  <si>
-    <t>0.0010,0.9808,0.0028,0.0997</t>
-  </si>
-  <si>
-    <t>0.0248,0.9014,0.0649,0.1145</t>
-  </si>
-  <si>
-    <t>0.0026,0.8816,0.7814,0.0014</t>
-  </si>
-  <si>
-    <t>0.1082,0.8919,0.0882,0.0047</t>
-  </si>
-  <si>
-    <t>0.7054,0.3400,0.0280,0.0069</t>
-  </si>
-  <si>
-    <t>0.3639,0.7016,0.0401,0.0018</t>
-  </si>
-  <si>
-    <t>0.9772,0.0159,0.0032,0.0020</t>
-  </si>
-  <si>
-    <t>0.9826,0.0049,0.0009,0.0061</t>
-  </si>
-  <si>
-    <t>0.9842,0.0085,0.0029,0.0018</t>
-  </si>
-  <si>
-    <t>0.9597,0.0314,0.0099,0.0036</t>
-  </si>
-  <si>
-    <t>0.9848,0.0097,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.8469,0.0371,0.1491,0.0054</t>
-  </si>
-  <si>
-    <t>0.9725,0.0066,0.0058,0.0086</t>
-  </si>
-  <si>
-    <t>0.9762,0.0138,0.0063,0.0026</t>
-  </si>
-  <si>
-    <t>0.0041,0.7821,0.8933,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.7436,0.9222,0.0002</t>
-  </si>
-  <si>
-    <t>0.0295,0.5843,0.6570,0.0017</t>
-  </si>
-  <si>
-    <t>0.0381,0.0605,0.9416,0.0017</t>
-  </si>
-  <si>
-    <t>0.7665,0.0528,0.0898,0.1011</t>
-  </si>
-  <si>
-    <t>0.5754,0.1374,0.3447,0.0240</t>
-  </si>
-  <si>
-    <t>0.2969,0.0128,0.8020,0.0042</t>
-  </si>
-  <si>
-    <t>0.6566,0.1570,0.1507,0.0857</t>
-  </si>
-  <si>
-    <t>0.2233,0.0048,0.0004,0.9075</t>
-  </si>
-  <si>
-    <t>0.0030,0.0006,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0005,0.5009,0.0005,0.9922</t>
-  </si>
-  <si>
-    <t>0.0268,0.0045,0.0028,0.9864</t>
-  </si>
-  <si>
-    <t>0.0033,0.6065,0.9336,0.0016</t>
-  </si>
-  <si>
-    <t>0.9658,0.0292,0.0050,0.0019</t>
-  </si>
-  <si>
-    <t>0.3627,0.6741,0.0329,0.0198</t>
-  </si>
-  <si>
-    <t>0.9807,0.0089,0.0012,0.0029</t>
-  </si>
-  <si>
-    <t>0.5906,0.5105,0.0307,0.0015</t>
-  </si>
-  <si>
-    <t>0.9783,0.0090,0.0026,0.0037</t>
-  </si>
-  <si>
-    <t>0.8013,0.0213,0.0650,0.1295</t>
-  </si>
-  <si>
-    <t>0.9386,0.0275,0.0163,0.0115</t>
-  </si>
-  <si>
-    <t>0.0007,0.0448,0.9871,0.0094</t>
-  </si>
-  <si>
-    <t>0.9396,0.0074,0.0129,0.0262</t>
-  </si>
-  <si>
-    <t>0.9835,0.0034,0.0010,0.0054</t>
-  </si>
-  <si>
-    <t>0.4923,0.5898,0.0321,0.0111</t>
-  </si>
-  <si>
-    <t>0.9247,0.0564,0.0084,0.0055</t>
-  </si>
-  <si>
-    <t>0.8905,0.0745,0.0375,0.0060</t>
-  </si>
-  <si>
-    <t>0.5395,0.4532,0.0316,0.0327</t>
-  </si>
-  <si>
-    <t>0.8470,0.1092,0.0567,0.0032</t>
-  </si>
-  <si>
-    <t>0.8958,0.0764,0.0310,0.0029</t>
-  </si>
-  <si>
-    <t>0.9840,0.0108,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9829,0.0102,0.0010,0.0023</t>
-  </si>
-  <si>
-    <t>0.9890,0.0060,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9842,0.0088,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.9864,0.0076,0.0015,0.0016</t>
-  </si>
-  <si>
-    <t>0.9741,0.0180,0.0031,0.0029</t>
-  </si>
-  <si>
-    <t>0.9833,0.0058,0.0006,0.0039</t>
-  </si>
-  <si>
-    <t>0.9851,0.0114,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.7032,0.4026,0.0111,0.0037</t>
-  </si>
-  <si>
-    <t>0.2100,0.8248,0.0499,0.0017</t>
-  </si>
-  <si>
-    <t>0.1711,0.8765,0.0100,0.0017</t>
-  </si>
-  <si>
-    <t>0.0541,0.7864,0.4705,0.0018</t>
-  </si>
-  <si>
-    <t>0.9469,0.0563,0.0058,0.0024</t>
-  </si>
-  <si>
-    <t>0.8404,0.1423,0.0537,0.0127</t>
-  </si>
-  <si>
-    <t>0.8379,0.2269,0.0161,0.0045</t>
-  </si>
-  <si>
-    <t>0.7691,0.3329,0.0175,0.0020</t>
-  </si>
-  <si>
-    <t>0.0061,0.0278,0.9874,0.0045</t>
-  </si>
-  <si>
-    <t>0.8698,0.1444,0.0284,0.0048</t>
-  </si>
-  <si>
-    <t>0.0007,0.0031,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.0157,0.9899,0.0003</t>
-  </si>
-  <si>
-    <t>0.0583,0.0147,0.9496,0.0024</t>
-  </si>
-  <si>
-    <t>0.0143,0.0358,0.9683,0.0058</t>
-  </si>
-  <si>
-    <t>0.2022,0.0087,0.8584,0.0057</t>
-  </si>
-  <si>
-    <t>0.0018,0.0021,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0042,0.0498,0.9880,0.0006</t>
-  </si>
-  <si>
-    <t>0.2791,0.2740,0.4786,0.0092</t>
-  </si>
-  <si>
-    <t>0.4347,0.0891,0.5510,0.0096</t>
-  </si>
-  <si>
-    <t>0.4119,0.0248,0.7227,0.0041</t>
-  </si>
-  <si>
-    <t>0.2300,0.1670,0.6466,0.0054</t>
-  </si>
-  <si>
-    <t>0.2503,0.4452,0.4016,0.0255</t>
-  </si>
-  <si>
-    <t>0.0637,0.5105,0.5357,0.0056</t>
-  </si>
-  <si>
-    <t>0.8387,0.0204,0.1132,0.0231</t>
-  </si>
-  <si>
-    <t>0.5543,0.2030,0.3061,0.0199</t>
-  </si>
-  <si>
-    <t>0.4098,0.7253,0.0133,0.0013</t>
-  </si>
-  <si>
-    <t>0.1236,0.8984,0.0146,0.0013</t>
-  </si>
-  <si>
-    <t>0.1936,0.8368,0.0349,0.0013</t>
-  </si>
-  <si>
-    <t>0.9126,0.1551,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.4851,0.6119,0.0280,0.0025</t>
-  </si>
-  <si>
-    <t>0.5413,0.1590,0.3147,0.0105</t>
-  </si>
-  <si>
-    <t>0.7309,0.0466,0.2657,0.0167</t>
-  </si>
-  <si>
-    <t>0.7897,0.0227,0.0138,0.1484</t>
-  </si>
-  <si>
-    <t>0.6250,0.0515,0.4033,0.0264</t>
-  </si>
-  <si>
-    <t>0.7005,0.0295,0.3275,0.0237</t>
-  </si>
-  <si>
-    <t>0.0132,0.0062,0.9654,0.0295</t>
-  </si>
-  <si>
-    <t>0.0445,0.0153,0.9493,0.0038</t>
-  </si>
-  <si>
-    <t>0.0125,0.1947,0.9537,0.0051</t>
-  </si>
-  <si>
-    <t>0.1013,0.0526,0.8911,0.0014</t>
-  </si>
-  <si>
-    <t>0.0450,0.2904,0.8022,0.0283</t>
-  </si>
-  <si>
-    <t>0.9933,0.0022,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9892,0.0057,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9860,0.0164,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9818,0.0121,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.9751,0.0219,0.0013,0.0023</t>
-  </si>
-  <si>
-    <t>0.9841,0.0226,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9859,0.0061,0.0017,0.0027</t>
-  </si>
-  <si>
-    <t>0.9821,0.0148,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.0248,0.0086,0.9698,0.0051</t>
-  </si>
-  <si>
-    <t>0.1811,0.4791,0.4828,0.0062</t>
-  </si>
-  <si>
-    <t>0.9127,0.0223,0.0419,0.0209</t>
-  </si>
-  <si>
-    <t>0.0113,0.0067,0.9869,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0029,0.9960,0.0006</t>
-  </si>
-  <si>
-    <t>0.0223,0.0203,0.9639,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0472,0.0464,0.9159,0.0027</t>
-  </si>
-  <si>
-    <t>0.0038,0.0163,0.9923,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.0163,0.9863,0.0011</t>
-  </si>
-  <si>
-    <t>0.0801,0.0385,0.8792,0.0393</t>
-  </si>
-  <si>
-    <t>0.3180,0.2833,0.4481,0.0122</t>
-  </si>
-  <si>
-    <t>0.6939,0.0271,0.3203,0.0243</t>
-  </si>
-  <si>
-    <t>0.8126,0.0335,0.1650,0.0098</t>
-  </si>
-  <si>
-    <t>0.9523,0.0557,0.0065,0.0024</t>
-  </si>
-  <si>
-    <t>0.9694,0.0467,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9944,0.0018,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9669,0.0334,0.0037,0.0023</t>
-  </si>
-  <si>
-    <t>0.9864,0.0030,0.0005,0.0048</t>
-  </si>
-  <si>
-    <t>0.9779,0.0219,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.9885,0.0092,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9658,0.0202,0.0038,0.0074</t>
-  </si>
-  <si>
-    <t>0.0524,0.0572,0.8899,0.0071</t>
-  </si>
-  <si>
-    <t>0.0056,0.4045,0.9427,0.0019</t>
-  </si>
-  <si>
-    <t>0.0043,0.4276,0.9378,0.0007</t>
-  </si>
-  <si>
-    <t>0.0643,0.1146,0.8462,0.0008</t>
-  </si>
-  <si>
-    <t>0.0064,0.0022,0.9880,0.0036</t>
-  </si>
-  <si>
-    <t>0.0444,0.0067,0.9061,0.0661</t>
-  </si>
-  <si>
-    <t>0.1436,0.0383,0.8273,0.0328</t>
-  </si>
-  <si>
-    <t>0.0999,0.0859,0.6757,0.2581</t>
-  </si>
-  <si>
-    <t>0.9062,0.0038,0.0053,0.0801</t>
-  </si>
-  <si>
-    <t>0.1173,0.0092,0.0003,0.9450</t>
-  </si>
-  <si>
-    <t>0.0272,0.0033,0.0036,0.9847</t>
-  </si>
-  <si>
-    <t>0.0030,0.0009,0.0003,0.9982</t>
-  </si>
-  <si>
-    <t>0.0149,0.0003,0.0000,0.9961</t>
-  </si>
-  <si>
-    <t>0.5813,0.0065,0.0430,0.3691</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8709,0.0784,0.0351,0.0145</t>
+  </si>
+  <si>
+    <t>0.1349,0.0006,0.0001,0.9641</t>
+  </si>
+  <si>
+    <t>0.5947,0.0255,0.0074,0.4575</t>
+  </si>
+  <si>
+    <t>0.0883,0.0100,0.0030,0.9585</t>
+  </si>
+  <si>
+    <t>0.9936,0.0071,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0028,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9702,0.0213,0.0089,0.0022</t>
+  </si>
+  <si>
+    <t>0.9808,0.0185,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.9847,0.0187,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9107,0.1688,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9890,0.0099,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9929,0.0049,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.6347,0.0947,0.3295,0.0205</t>
+  </si>
+  <si>
+    <t>0.2347,0.0939,0.7571,0.0032</t>
+  </si>
+  <si>
+    <t>0.2302,0.0269,0.8470,0.0008</t>
+  </si>
+  <si>
+    <t>0.2334,0.0120,0.8463,0.0047</t>
+  </si>
+  <si>
+    <t>0.8179,0.0441,0.1387,0.0147</t>
+  </si>
+  <si>
+    <t>0.0057,0.9842,0.0141,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.9909,0.0106,0.0007</t>
+  </si>
+  <si>
+    <t>0.2135,0.8146,0.0229,0.0058</t>
+  </si>
+  <si>
+    <t>0.0307,0.9641,0.0073,0.0013</t>
+  </si>
+  <si>
+    <t>0.0100,0.9797,0.0088,0.0021</t>
+  </si>
+  <si>
+    <t>0.5061,0.0039,0.6616,0.0053</t>
+  </si>
+  <si>
+    <t>0.0461,0.0042,0.9496,0.0075</t>
+  </si>
+  <si>
+    <t>0.0407,0.0031,0.9701,0.0016</t>
+  </si>
+  <si>
+    <t>0.1084,0.0105,0.9132,0.0046</t>
+  </si>
+  <si>
+    <t>0.0380,0.0027,0.9741,0.0013</t>
+  </si>
+  <si>
+    <t>0.1097,0.0081,0.8820,0.0208</t>
+  </si>
+  <si>
+    <t>0.0119,0.0018,0.9830,0.0030</t>
+  </si>
+  <si>
+    <t>0.7855,0.2065,0.0488,0.0069</t>
+  </si>
+  <si>
+    <t>0.9273,0.0377,0.0355,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.0094,0.9915,0.0088</t>
+  </si>
+  <si>
+    <t>0.0193,0.8045,0.4648,0.0009</t>
+  </si>
+  <si>
+    <t>0.7460,0.2593,0.0263,0.0206</t>
+  </si>
+  <si>
+    <t>0.8378,0.1273,0.0549,0.0127</t>
+  </si>
+  <si>
+    <t>0.7652,0.3432,0.0129,0.0018</t>
+  </si>
+  <si>
+    <t>0.0151,0.9416,0.3633,0.0011</t>
+  </si>
+  <si>
+    <t>0.0322,0.5654,0.7886,0.0131</t>
+  </si>
+  <si>
+    <t>0.0238,0.0534,0.9266,0.0451</t>
+  </si>
+  <si>
+    <t>0.0175,0.0435,0.9677,0.0033</t>
+  </si>
+  <si>
+    <t>0.1014,0.0112,0.9064,0.0120</t>
+  </si>
+  <si>
+    <t>0.0291,0.0768,0.9561,0.0023</t>
+  </si>
+  <si>
+    <t>0.0169,0.9149,0.1542,0.0080</t>
+  </si>
+  <si>
+    <t>0.0182,0.0068,0.9694,0.0097</t>
+  </si>
+  <si>
+    <t>0.0722,0.2762,0.0043,0.8665</t>
+  </si>
+  <si>
+    <t>0.0040,0.9560,0.0130,0.0922</t>
+  </si>
+  <si>
+    <t>0.0168,0.9141,0.3214,0.0034</t>
+  </si>
+  <si>
+    <t>0.0064,0.9747,0.0622,0.0064</t>
+  </si>
+  <si>
+    <t>0.0071,0.0709,0.9792,0.0046</t>
+  </si>
+  <si>
+    <t>0.0048,0.0987,0.9830,0.0007</t>
+  </si>
+  <si>
+    <t>0.0210,0.0026,0.9661,0.0126</t>
+  </si>
+  <si>
+    <t>0.0553,0.0123,0.9421,0.0070</t>
+  </si>
+  <si>
+    <t>0.0557,0.0463,0.9011,0.0086</t>
+  </si>
+  <si>
+    <t>0.0073,0.1611,0.9436,0.0042</t>
+  </si>
+  <si>
+    <t>0.6844,0.4516,0.0140,0.0013</t>
+  </si>
+  <si>
+    <t>0.9351,0.0366,0.0372,0.0054</t>
+  </si>
+  <si>
+    <t>0.9616,0.0175,0.0077,0.0094</t>
+  </si>
+  <si>
+    <t>0.0030,0.0668,0.9898,0.0030</t>
+  </si>
+  <si>
+    <t>0.9828,0.0131,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9826,0.0185,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9492,0.0636,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.0052,0.7307,0.9315,0.0027</t>
+  </si>
+  <si>
+    <t>0.0114,0.0264,0.9667,0.0134</t>
+  </si>
+  <si>
+    <t>0.0198,0.0110,0.9607,0.0111</t>
+  </si>
+  <si>
+    <t>0.0012,0.8934,0.9481,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0012,0.9974,0.0013</t>
+  </si>
+  <si>
+    <t>0.0078,0.8925,0.4807,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.9852,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.8331,0.0990,0.0745,0.0082</t>
+  </si>
+  <si>
+    <t>0.6245,0.1769,0.2953,0.0048</t>
+  </si>
+  <si>
+    <t>0.0160,0.0815,0.9662,0.0037</t>
+  </si>
+  <si>
+    <t>0.0013,0.7156,0.9732,0.0001</t>
+  </si>
+  <si>
+    <t>0.0063,0.6190,0.9033,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.9908,0.5654,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.8755,0.8887,0.0005</t>
+  </si>
+  <si>
+    <t>0.0299,0.0008,0.0397,0.9561</t>
+  </si>
+  <si>
+    <t>0.0111,0.0027,0.0002,0.9952</t>
+  </si>
+  <si>
+    <t>0.0110,0.0023,0.0002,0.9956</t>
+  </si>
+  <si>
+    <t>0.0131,0.0043,0.0008,0.9929</t>
+  </si>
+  <si>
+    <t>0.0140,0.0075,0.0015,0.9925</t>
+  </si>
+  <si>
+    <t>0.0142,0.0066,0.0003,0.9936</t>
+  </si>
+  <si>
+    <t>0.0012,0.9789,0.5327,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.8908,0.9426,0.0003</t>
+  </si>
+  <si>
+    <t>0.0139,0.5099,0.8853,0.0058</t>
+  </si>
+  <si>
+    <t>0.0041,0.1811,0.9783,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9657,0.7133,0.0002</t>
+  </si>
+  <si>
+    <t>0.0064,0.7249,0.8720,0.0012</t>
+  </si>
+  <si>
+    <t>0.9824,0.0236,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9117,0.1705,0.0052,0.0010</t>
+  </si>
+  <si>
+    <t>0.9616,0.0490,0.0042,0.0012</t>
+  </si>
+  <si>
+    <t>0.9803,0.0207,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9631,0.0501,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.9786,0.0138,0.0043,0.0026</t>
+  </si>
+  <si>
+    <t>0.9877,0.0082,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9770,0.0292,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0028,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9872,0.0089,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9856,0.0116,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9904,0.0053,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0029,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0565,0.0036,0.9473,0.0083</t>
+  </si>
+  <si>
+    <t>0.0460,0.0077,0.9526,0.0029</t>
+  </si>
+  <si>
+    <t>0.6745,0.0613,0.3130,0.0361</t>
+  </si>
+  <si>
+    <t>0.2559,0.0209,0.8361,0.0024</t>
+  </si>
+  <si>
+    <t>0.0148,0.9726,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.0073,0.9833,0.0032,0.0020</t>
+  </si>
+  <si>
+    <t>0.0655,0.9133,0.0136,0.0138</t>
+  </si>
+  <si>
+    <t>0.1175,0.9018,0.0106,0.0017</t>
+  </si>
+  <si>
+    <t>0.0241,0.9571,0.0156,0.0049</t>
+  </si>
+  <si>
+    <t>0.0026,0.9920,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.1387,0.8653,0.0386,0.0022</t>
+  </si>
+  <si>
+    <t>0.7178,0.1062,0.1093,0.0723</t>
+  </si>
+  <si>
+    <t>0.4763,0.0018,0.7612,0.0026</t>
+  </si>
+  <si>
+    <t>0.5494,0.1466,0.3497,0.0199</t>
+  </si>
+  <si>
+    <t>0.2927,0.0307,0.7435,0.0069</t>
+  </si>
+  <si>
+    <t>0.3659,0.0227,0.0349,0.7073</t>
+  </si>
+  <si>
+    <t>0.0019,0.9911,0.0709,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.9897,0.0056,0.0061</t>
+  </si>
+  <si>
+    <t>0.0223,0.9178,0.0279,0.1161</t>
+  </si>
+  <si>
+    <t>0.0016,0.8994,0.9044,0.0007</t>
+  </si>
+  <si>
+    <t>0.0318,0.9511,0.0991,0.0010</t>
+  </si>
+  <si>
+    <t>0.4337,0.6266,0.0351,0.0024</t>
+  </si>
+  <si>
+    <t>0.4662,0.5986,0.0447,0.0040</t>
+  </si>
+  <si>
+    <t>0.9729,0.0154,0.0048,0.0031</t>
+  </si>
+  <si>
+    <t>0.9905,0.0034,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9910,0.0028,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.9690,0.0162,0.0095,0.0040</t>
+  </si>
+  <si>
+    <t>0.9912,0.0036,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9298,0.0309,0.0325,0.0142</t>
+  </si>
+  <si>
+    <t>0.9755,0.0107,0.0040,0.0048</t>
+  </si>
+  <si>
+    <t>0.9772,0.0085,0.0052,0.0055</t>
+  </si>
+  <si>
+    <t>0.0173,0.0843,0.9639,0.0022</t>
+  </si>
+  <si>
+    <t>0.0025,0.6233,0.9470,0.0002</t>
+  </si>
+  <si>
+    <t>0.0230,0.5716,0.7788,0.0037</t>
+  </si>
+  <si>
+    <t>0.0295,0.0325,0.9640,0.0008</t>
+  </si>
+  <si>
+    <t>0.8001,0.0164,0.2083,0.0140</t>
+  </si>
+  <si>
+    <t>0.4954,0.3618,0.0978,0.0994</t>
+  </si>
+  <si>
+    <t>0.1568,0.0032,0.9218,0.0024</t>
+  </si>
+  <si>
+    <t>0.6623,0.2321,0.0585,0.0426</t>
+  </si>
+  <si>
+    <t>0.1796,0.0117,0.0011,0.9195</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0049,0.0187,0.0002,0.9963</t>
+  </si>
+  <si>
+    <t>0.0807,0.0019,0.0016,0.9699</t>
+  </si>
+  <si>
+    <t>0.0046,0.7450,0.8791,0.0019</t>
+  </si>
+  <si>
+    <t>0.9810,0.0137,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.1114,0.8775,0.0134,0.0068</t>
+  </si>
+  <si>
+    <t>0.9740,0.0176,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.3684,0.6045,0.1046,0.0033</t>
+  </si>
+  <si>
+    <t>0.9304,0.0508,0.0171,0.0074</t>
+  </si>
+  <si>
+    <t>0.5383,0.0226,0.0052,0.6030</t>
+  </si>
+  <si>
+    <t>0.9464,0.0292,0.0118,0.0086</t>
+  </si>
+  <si>
+    <t>0.0045,0.1780,0.9623,0.0140</t>
+  </si>
+  <si>
+    <t>0.8988,0.0016,0.0149,0.0530</t>
+  </si>
+  <si>
+    <t>0.9348,0.0103,0.0246,0.0250</t>
+  </si>
+  <si>
+    <t>0.7210,0.2320,0.0222,0.0506</t>
+  </si>
+  <si>
+    <t>0.9021,0.0414,0.0309,0.0049</t>
+  </si>
+  <si>
+    <t>0.7146,0.2589,0.0837,0.0141</t>
+  </si>
+  <si>
+    <t>0.1263,0.6406,0.2989,0.0230</t>
+  </si>
+  <si>
+    <t>0.7604,0.1774,0.0829,0.0031</t>
+  </si>
+  <si>
+    <t>0.5284,0.4652,0.0760,0.0032</t>
+  </si>
+  <si>
+    <t>0.9847,0.0121,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9807,0.0183,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9898,0.0031,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.9751,0.0155,0.0030,0.0036</t>
+  </si>
+  <si>
+    <t>0.9781,0.0128,0.0025,0.0025</t>
+  </si>
+  <si>
+    <t>0.9646,0.0403,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9894,0.0032,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.9811,0.0084,0.0024,0.0043</t>
+  </si>
+  <si>
+    <t>0.4932,0.6209,0.0159,0.0079</t>
+  </si>
+  <si>
+    <t>0.4808,0.6610,0.0153,0.0015</t>
+  </si>
+  <si>
+    <t>0.1264,0.8776,0.0118,0.0075</t>
+  </si>
+  <si>
+    <t>0.0841,0.3289,0.8340,0.0060</t>
+  </si>
+  <si>
+    <t>0.9728,0.0174,0.0028,0.0032</t>
+  </si>
+  <si>
+    <t>0.5952,0.4478,0.0508,0.0041</t>
+  </si>
+  <si>
+    <t>0.9538,0.0228,0.0088,0.0090</t>
+  </si>
+  <si>
+    <t>0.8290,0.2150,0.0290,0.0056</t>
+  </si>
+  <si>
+    <t>0.0017,0.4672,0.9821,0.0002</t>
+  </si>
+  <si>
+    <t>0.7484,0.1617,0.1371,0.0067</t>
+  </si>
+  <si>
+    <t>0.0039,0.0031,0.9932,0.0007</t>
+  </si>
+  <si>
+    <t>0.0138,0.1417,0.9465,0.0104</t>
+  </si>
+  <si>
+    <t>0.2087,0.0068,0.9001,0.0013</t>
+  </si>
+  <si>
+    <t>0.0333,0.0981,0.9210,0.0123</t>
+  </si>
+  <si>
+    <t>0.0492,0.0134,0.9607,0.0014</t>
+  </si>
+  <si>
+    <t>0.0407,0.0014,0.9748,0.0013</t>
+  </si>
+  <si>
+    <t>0.0189,0.0049,0.9743,0.0050</t>
+  </si>
+  <si>
+    <t>0.4289,0.0553,0.6145,0.0072</t>
+  </si>
+  <si>
+    <t>0.2955,0.0128,0.8279,0.0020</t>
+  </si>
+  <si>
+    <t>0.3892,0.2959,0.3818,0.0082</t>
+  </si>
+  <si>
+    <t>0.1575,0.0999,0.7880,0.0010</t>
+  </si>
+  <si>
+    <t>0.1923,0.2118,0.6242,0.0022</t>
+  </si>
+  <si>
+    <t>0.5820,0.0159,0.5839,0.0035</t>
+  </si>
+  <si>
+    <t>0.5267,0.0465,0.5203,0.0195</t>
+  </si>
+  <si>
+    <t>0.5362,0.1429,0.3656,0.0287</t>
+  </si>
+  <si>
+    <t>0.8585,0.2653,0.0060,0.0009</t>
+  </si>
+  <si>
+    <t>0.5905,0.5905,0.0088,0.0012</t>
+  </si>
+  <si>
+    <t>0.7114,0.3952,0.0095,0.0078</t>
+  </si>
+  <si>
+    <t>0.9173,0.1332,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.9074,0.1413,0.0079,0.0027</t>
+  </si>
+  <si>
+    <t>0.4900,0.0892,0.5214,0.0089</t>
+  </si>
+  <si>
+    <t>0.7886,0.0076,0.3254,0.0044</t>
+  </si>
+  <si>
+    <t>0.7476,0.0216,0.3156,0.0101</t>
+  </si>
+  <si>
+    <t>0.2620,0.0175,0.6770,0.0770</t>
+  </si>
+  <si>
+    <t>0.8745,0.0191,0.0748,0.0184</t>
+  </si>
+  <si>
+    <t>0.0290,0.0338,0.9183,0.0713</t>
+  </si>
+  <si>
+    <t>0.0529,0.1978,0.8567,0.0070</t>
+  </si>
+  <si>
+    <t>0.0070,0.4877,0.9416,0.0012</t>
+  </si>
+  <si>
+    <t>0.0986,0.0196,0.8926,0.0107</t>
+  </si>
+  <si>
+    <t>0.1004,0.1415,0.8250,0.0083</t>
+  </si>
+  <si>
+    <t>0.9892,0.0063,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9341,0.0859,0.0079,0.0015</t>
+  </si>
+  <si>
+    <t>0.9766,0.0200,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9494,0.0618,0.0073,0.0014</t>
+  </si>
+  <si>
+    <t>0.9550,0.0615,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.9797,0.0165,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9826,0.0078,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.9317,0.0877,0.0103,0.0025</t>
+  </si>
+  <si>
+    <t>0.1436,0.0190,0.9084,0.0040</t>
+  </si>
+  <si>
+    <t>0.1185,0.6922,0.4045,0.0067</t>
+  </si>
+  <si>
+    <t>0.5489,0.4327,0.0731,0.0283</t>
+  </si>
+  <si>
+    <t>0.0034,0.1082,0.9843,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0195,0.9880,0.0015</t>
+  </si>
+  <si>
+    <t>0.0209,0.0244,0.9650,0.0015</t>
+  </si>
+  <si>
+    <t>0.0010,0.0025,0.9952,0.0030</t>
+  </si>
+  <si>
+    <t>0.0342,0.0243,0.9528,0.0042</t>
+  </si>
+  <si>
+    <t>0.0012,0.0115,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0300,0.0215,0.9611,0.0016</t>
+  </si>
+  <si>
+    <t>0.7694,0.0364,0.2195,0.0160</t>
+  </si>
+  <si>
+    <t>0.7318,0.0484,0.1459,0.0522</t>
+  </si>
+  <si>
+    <t>0.4893,0.0052,0.6533,0.0065</t>
+  </si>
+  <si>
+    <t>0.8148,0.0155,0.1048,0.0405</t>
+  </si>
+  <si>
+    <t>0.9872,0.0082,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9741,0.0313,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.9810,0.0227,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9716,0.0341,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.9918,0.0016,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9752,0.0326,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9852,0.0142,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9818,0.0116,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.0236,0.1042,0.9314,0.0026</t>
+  </si>
+  <si>
+    <t>0.0096,0.0083,0.9804,0.0052</t>
+  </si>
+  <si>
+    <t>0.0046,0.6443,0.8900,0.0005</t>
+  </si>
+  <si>
+    <t>0.0368,0.1305,0.9012,0.0050</t>
+  </si>
+  <si>
+    <t>0.0111,0.0100,0.9774,0.0060</t>
+  </si>
+  <si>
+    <t>0.5667,0.0542,0.2956,0.1355</t>
+  </si>
+  <si>
+    <t>0.0947,0.0113,0.9140,0.0104</t>
+  </si>
+  <si>
+    <t>0.0070,0.0268,0.9751,0.0141</t>
+  </si>
+  <si>
+    <t>0.6868,0.0041,0.0469,0.2478</t>
+  </si>
+  <si>
+    <t>0.0707,0.0095,0.0006,0.9727</t>
+  </si>
+  <si>
+    <t>0.1007,0.0157,0.0083,0.9411</t>
+  </si>
+  <si>
+    <t>0.0108,0.0010,0.0005,0.9953</t>
+  </si>
+  <si>
+    <t>0.0248,0.0005,0.0003,0.9914</t>
+  </si>
+  <si>
+    <t>0.7178,0.0788,0.0349,0.1775</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2584,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,10 +3981,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,10 +5367,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
